--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487851_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487851_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7102</v>
+        <v>8.1433</v>
       </c>
       <c r="E2" t="n">
-        <v>9.223000000000001</v>
+        <v>8.6267</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5128</v>
+        <v>-0.4835</v>
       </c>
       <c r="G2" t="n">
         <v>9.261900000000001</v>
@@ -610,13 +610,13 @@
         <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8646</v>
+        <v>1.2976</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2297</v>
+        <v>0.6334</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6348</v>
+        <v>0.6642</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1675</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2637</v>
+        <v>6.3951</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0141</v>
+        <v>5.2702</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2496</v>
+        <v>1.1249</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1377</v>
+        <v>3.588</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3599</v>
+        <v>-0.2321</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2222</v>
+        <v>3.82</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7503</v>
+        <v>3.9597</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5152</v>
+        <v>0.4989</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2351</v>
+        <v>3.4608</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6126</v>
+        <v>-0.3717</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1553</v>
+        <v>-0.731</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4573</v>
+        <v>0.3592</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1042</v>
+        <v>1.161</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4907</v>
+        <v>0.4968</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6135</v>
+        <v>0.6642</v>
       </c>
       <c r="V3" t="n">
         <v>0.8137</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3843</v>
+        <v>6.2587</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2888</v>
+        <v>5.5669</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0956</v>
+        <v>0.6917</v>
       </c>
       <c r="G4" t="n">
-        <v>3.588</v>
+        <v>3.1377</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2321</v>
+        <v>4.3599</v>
       </c>
       <c r="I4" t="n">
-        <v>3.82</v>
+        <v>-1.2222</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9597</v>
+        <v>4.7503</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4989</v>
+        <v>4.5152</v>
       </c>
       <c r="L4" t="n">
-        <v>3.4608</v>
+        <v>0.2351</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3717</v>
+        <v>-1.6126</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.731</v>
+        <v>-0.1553</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3592</v>
+        <v>-1.4573</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1502</v>
+        <v>2.0991</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5153</v>
+        <v>1.0435</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6348</v>
+        <v>1.0557</v>
       </c>
       <c r="V4" t="n">
         <v>0.8137</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>L. PAUL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9174</v>
+        <v>4.2629</v>
       </c>
       <c r="E5" t="n">
-        <v>3.546</v>
+        <v>5.2453</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3714</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0108</v>
+        <v>2.8119</v>
       </c>
       <c r="H5" t="n">
-        <v>3.659</v>
+        <v>2.4755</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6482</v>
+        <v>0.3364</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2847</v>
+        <v>4.3265</v>
       </c>
       <c r="K5" t="n">
-        <v>4.0103</v>
+        <v>2.5328</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2743</v>
+        <v>1.7937</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2739</v>
+        <v>-1.5146</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3513</v>
+        <v>-0.0573</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9225</v>
+        <v>-1.4573</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>1.738</v>
+        <v>0.2835</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3196</v>
+        <v>-0.0219</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4184</v>
+        <v>0.3054</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2477</v>
+        <v>1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0177</v>
+        <v>1.9813</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.23</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. PAUL</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2065</v>
+        <v>4.0064</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3944</v>
+        <v>3.0754</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1879</v>
+        <v>0.931</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8119</v>
+        <v>3.0108</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4755</v>
+        <v>3.659</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3364</v>
+        <v>-0.6482</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3265</v>
+        <v>4.2847</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5328</v>
+        <v>4.0103</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7937</v>
+        <v>0.2743</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5146</v>
+        <v>-1.2739</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0573</v>
+        <v>-0.3513</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4573</v>
+        <v>-0.9225</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>0.227</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1272</v>
+        <v>-0.1509</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0998</v>
+        <v>0.978</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1675</v>
+        <v>-0.2477</v>
       </c>
       <c r="W6" t="n">
-        <v>1.9813</v>
+        <v>-0.0177</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8137</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8195</v>
+        <v>2.0147</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0185</v>
+        <v>1.1257</v>
       </c>
       <c r="F7" t="n">
-        <v>0.801</v>
+        <v>0.8891</v>
       </c>
       <c r="G7" t="n">
         <v>1.7732</v>
@@ -1000,13 +1000,13 @@
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3699</v>
+        <v>-0.1747</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0216</v>
+        <v>0.1096</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5978</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6772</v>
+        <v>0.7839</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0794</v>
+        <v>-0.0677</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6615</v>
+        <v>-0.1731</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3178</v>
+        <v>-1.8467</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3437</v>
+        <v>1.6737</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.351</v>
+        <v>0.7131</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6442</v>
+        <v>-1.0626</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2932</v>
+        <v>1.7757</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3105</v>
+        <v>-0.8862</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3265</v>
+        <v>-0.7841</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6369</v>
+        <v>-0.102</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3308</v>
+        <v>0.6811</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3262</v>
+        <v>-0.0562</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0045</v>
+        <v>0.7373</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3538</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6076</v>
+        <v>-0.1296</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3344</v>
+        <v>-0.3558</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2732</v>
+        <v>0.2262</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1731</v>
+        <v>-1.6615</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8467</v>
+        <v>-1.3178</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6737</v>
+        <v>-0.3437</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7131</v>
+        <v>-0.351</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0626</v>
+        <v>-1.6442</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7757</v>
+        <v>1.2932</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8862</v>
+        <v>-1.3105</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7841</v>
+        <v>0.3265</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.102</v>
+        <v>-1.6369</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6425999999999999</v>
+        <v>0.1375</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1744</v>
+        <v>-0.0047</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.1423</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8362</v>
+        <v>-2.6299</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1528</v>
+        <v>-3.0346</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3166</v>
+        <v>0.4046</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9108</v>
@@ -1234,13 +1234,13 @@
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7985</v>
+        <v>0.4078</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1091</v>
+        <v>0.0091</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3106</v>
+        <v>0.3987</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5838</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0752</v>
+        <v>-3.5482</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6226</v>
+        <v>-3.3012</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4525</v>
+        <v>-0.247</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1216</v>
@@ -1312,13 +1312,13 @@
         <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.475</v>
+        <v>0.052</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3262</v>
+        <v>-0.0047</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1487</v>
+        <v>0.0568</v>
       </c>
       <c r="V11" t="n">
         <v>-0.23</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>24.18480000000001</v>
+        <v>25.4896</v>
       </c>
       <c r="E12" t="n">
-        <v>21.6978</v>
+        <v>23.0025</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4872</v>
+        <v>2.4869</v>
       </c>
       <c r="G12" t="n">
         <v>15.7165</v>
@@ -1363,25 +1363,25 @@
         <v>9.266299999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>24.67900000000001</v>
+        <v>24.679</v>
       </c>
       <c r="K12" t="n">
-        <v>9.922099999999999</v>
+        <v>9.922099999999997</v>
       </c>
       <c r="L12" t="n">
         <v>14.7567</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.962299999999999</v>
+        <v>-8.962300000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-3.4719</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.490300000000001</v>
+        <v>-5.4903</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0811</v>
+        <v>2.081100000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-8.3248</v>
@@ -1390,16 +1390,16 @@
         <v>10.4059</v>
       </c>
       <c r="S12" t="n">
-        <v>5.4672</v>
+        <v>6.772</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3550999999999998</v>
+        <v>1.6601</v>
       </c>
       <c r="U12" t="n">
-        <v>5.112100000000001</v>
+        <v>5.1122</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9197000000000002</v>
+        <v>0.9196999999999997</v>
       </c>
       <c r="W12" t="n">
         <v>4.9885</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4868</v>
+        <v>1.9613</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4795</v>
+        <v>4.8366</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9927</v>
+        <v>-2.8753</v>
       </c>
       <c r="G13" t="n">
         <v>2.6475</v>
@@ -1468,13 +1468,13 @@
         <v>0.8325</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4313</v>
+        <v>-0.9568</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2544</v>
+        <v>-0.3886</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6856</v>
+        <v>-0.5682</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3538</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1564</v>
+        <v>0.3032</v>
       </c>
       <c r="E14" t="n">
         <v>0.08169999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0747</v>
+        <v>0.2215</v>
       </c>
       <c r="G14" t="n">
         <v>-0.531</v>
@@ -1546,13 +1546,13 @@
         <v>0.2081</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2284</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>-0.1833</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.045</v>
+        <v>0.1018</v>
       </c>
       <c r="V14" t="n">
         <v>0.7076</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9056999999999999</v>
+        <v>-0.2907</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8062</v>
+        <v>2.1276</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7119</v>
+        <v>-2.4183</v>
       </c>
       <c r="G15" t="n">
         <v>-1.2163</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7301</v>
+        <v>-0.115</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9539</v>
+        <v>-0.6324</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2238</v>
+        <v>0.5174</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2914</v>
+        <v>-1.0669</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7818</v>
+        <v>-1.6747</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4904</v>
+        <v>0.6078</v>
       </c>
       <c r="G16" t="n">
         <v>-0.823</v>
@@ -1702,13 +1702,13 @@
         <v>0.2081</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6765</v>
+        <v>-0.452</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2851</v>
+        <v>-0.1677</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4154</v>
+        <v>-1.8059</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5107</v>
+        <v>0.2964</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9261</v>
+        <v>-2.1023</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1361</v>
@@ -1780,13 +1780,13 @@
         <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4032</v>
+        <v>-0.7937</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2519</v>
+        <v>-0.4662</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1513</v>
+        <v>-0.3275</v>
       </c>
       <c r="V17" t="n">
         <v>-0.4599</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GAYE</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5422</v>
+        <v>-3.1014</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3279</v>
+        <v>-1.1928</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8701</v>
+        <v>-1.9086</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.2064</v>
+        <v>-1.6036</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6632</v>
+        <v>-1.6567</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.5433</v>
+        <v>0.0531</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.218</v>
+        <v>-0.0808</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.414</v>
+        <v>-0.738</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1959</v>
+        <v>0.6572</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.9884</v>
+        <v>-1.5228</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2492</v>
+        <v>-0.9187</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.7392</v>
+        <v>-0.6041</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R18" t="n">
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7672</v>
+        <v>-0.4978</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0215</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7458</v>
+        <v>-0.4045</v>
       </c>
       <c r="V18" t="n">
-        <v>2.1051</v>
+        <v>-0.5838</v>
       </c>
       <c r="W18" t="n">
-        <v>2.565</v>
+        <v>0.23</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4599</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>A. GAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9252</v>
+        <v>-3.1573</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4819</v>
+        <v>0.0064</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4432</v>
+        <v>-3.1637</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3579</v>
+        <v>-5.2064</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5969</v>
+        <v>-1.6632</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.761</v>
+        <v>-3.5433</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4101</v>
+        <v>-1.218</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1425</v>
+        <v>-1.414</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7323</v>
+        <v>0.1959</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7681</v>
+        <v>-3.9884</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7394</v>
+        <v>-0.2492</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0287</v>
+        <v>-3.7392</v>
       </c>
       <c r="P19" t="n">
         <v>-0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1292</v>
+        <v>0.1522</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6433</v>
+        <v>-0.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5142</v>
+        <v>0.4522</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.23</v>
+        <v>2.1051</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6768</v>
+        <v>-3.4918</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6214</v>
+        <v>-1.6962</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0554</v>
+        <v>-1.7956</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6036</v>
+        <v>-2.3579</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6567</v>
+        <v>-0.5969</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0531</v>
+        <v>-1.761</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0808</v>
+        <v>0.4101</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.738</v>
+        <v>1.1425</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6572</v>
+        <v>-0.7323</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5228</v>
+        <v>-2.7681</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9187</v>
+        <v>-1.7394</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6041</v>
+        <v>-1.0287</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.2487</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0732</v>
+        <v>-0.6958</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5219</v>
+        <v>-0.8577</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5513</v>
+        <v>0.1619</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8137</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8871</v>
+        <v>-4.6538</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1765</v>
+        <v>-0.855</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.7107</v>
+        <v>-3.7987</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9808</v>
@@ -2092,13 +2092,13 @@
         <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3851</v>
+        <v>-1.1517</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5411</v>
+        <v>-1.2196</v>
       </c>
       <c r="U21" t="n">
-        <v>0.156</v>
+        <v>0.0679</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9376</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.183999999999999</v>
+        <v>-8.881600000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6313</v>
+        <v>-4.417</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5527</v>
+        <v>-4.4646</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5089</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1776</v>
+        <v>-0.8752</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.901</v>
+        <v>-0.6867</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2766</v>
+        <v>-0.1885</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1675</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-24.1846</v>
+        <v>-24.1849</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.486900000000001</v>
+        <v>-2.487</v>
       </c>
       <c r="F23" t="n">
-        <v>-21.6977</v>
+        <v>-21.6978</v>
       </c>
       <c r="G23" t="n">
         <v>-15.7165</v>
@@ -2251,13 +2251,13 @@
         <v>-5.4674</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.112</v>
+        <v>-5.1121</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3551000000000001</v>
+        <v>-0.3552</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9198999999999997</v>
+        <v>-0.9198999999999995</v>
       </c>
       <c r="W23" t="n">
         <v>4.0686</v>
